--- a/registrations_export.xlsx
+++ b/registrations_export.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="232">
   <si>
     <t>S.No</t>
   </si>
@@ -45,6 +45,9 @@
     <t>Email Verified</t>
   </si>
   <si>
+    <t>Email Sent</t>
+  </si>
+  <si>
     <t>Has Entered</t>
   </si>
   <si>
@@ -129,6 +132,252 @@
     <t>24/2/2026, 8:22:10 pm</t>
   </si>
   <si>
+    <t>Mohit Suwalka</t>
+  </si>
+  <si>
+    <t>mohitsuwalka88783@gmail.com</t>
+  </si>
+  <si>
+    <t>8005961269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jk lakshmipat university </t>
+  </si>
+  <si>
+    <t>302026, jaipur</t>
+  </si>
+  <si>
+    <t>Badminton (Singles) (Boys)</t>
+  </si>
+  <si>
+    <t>7/3/2026, 3:29:35 pm</t>
+  </si>
+  <si>
+    <t>Deepshikha R</t>
+  </si>
+  <si>
+    <t>kav906ita@gmail.com</t>
+  </si>
+  <si>
+    <t>08003463226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kanoria collage </t>
+  </si>
+  <si>
+    <t>58 vrindavan colony jhotwara jaipur, Rajasthan</t>
+  </si>
+  <si>
+    <t>Volleyball (Girls)</t>
+  </si>
+  <si>
+    <t>7/3/2026, 10:31:22 pm</t>
+  </si>
+  <si>
+    <t>Shreya</t>
+  </si>
+  <si>
+    <t>Shreyasharma15102006@gmail.com</t>
+  </si>
+  <si>
+    <t>7500125414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swami rama Himalayan University </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Himalayan  Hospital  jollygrant  dheradun  Near sbi Atm Jolly Grant Dehradun </t>
+  </si>
+  <si>
+    <t>Basketball (Girls), Volleyball (Girls), Badminton (Singles) (Girls)</t>
+  </si>
+  <si>
+    <t>9/3/2026, 5:32:41 pm</t>
+  </si>
+  <si>
+    <t>Ruchika Mathur</t>
+  </si>
+  <si>
+    <t>ruchimathurcute2007@gmail.com</t>
+  </si>
+  <si>
+    <t>08619871879</t>
+  </si>
+  <si>
+    <t>Kanoria PG Mahila Mahavidyalaya</t>
+  </si>
+  <si>
+    <t>Jawahar Lal Nehru Marg, Near Gandhi Circle - Kanodiya Bus Stop, Bapu Nagar</t>
+  </si>
+  <si>
+    <t>Badminton (Singles) (Girls)</t>
+  </si>
+  <si>
+    <t>9/3/2026, 8:57:36 pm</t>
+  </si>
+  <si>
+    <t>Gunjan Choudhary</t>
+  </si>
+  <si>
+    <t>gunjan2003.choudhary@gmail.com</t>
+  </si>
+  <si>
+    <t>8278671820</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kanoria pg mahila Mahavidyalaya </t>
+  </si>
+  <si>
+    <t>Kanoria Pg Mahila Mahavidyalaya Main Campus, Kanoria Pg Mahila Mahavidyalaya, Jawahar Lal Nehru Marg, Bapu Nagar, Jaipur, Rajasthan 302015</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:27:20 pm</t>
+  </si>
+  <si>
+    <t>Sakshi Sharma</t>
+  </si>
+  <si>
+    <t>sakshisharmasakshi707@gmail.com</t>
+  </si>
+  <si>
+    <t>7850079584</t>
+  </si>
+  <si>
+    <t>Kanoria P G Mahila Mahavidyalaya</t>
+  </si>
+  <si>
+    <t>Jawahar Lal Nehru marg,  near Gandhi circle -Kanoria Bus stop, Bapu nagar-302015</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:29:43 pm</t>
+  </si>
+  <si>
+    <t>Chitman kaur</t>
+  </si>
+  <si>
+    <t>kaurchitman1@gmail.com</t>
+  </si>
+  <si>
+    <t>9799208648</t>
+  </si>
+  <si>
+    <t>Kanoria pg mahila mahavidayala</t>
+  </si>
+  <si>
+    <t>1200, barkat nagar kissan marg near Axis bank, jaipur</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:30:24 pm</t>
+  </si>
+  <si>
+    <t>Surbhi Sharma</t>
+  </si>
+  <si>
+    <t>surbhisharma22996@gmail.com</t>
+  </si>
+  <si>
+    <t>9079650130</t>
+  </si>
+  <si>
+    <t>Kanoria pg mahila mahavidyalay jaipur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175 parshvanath negar near airport sanganer jaipur </t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:32:23 pm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gehna Khandelwal </t>
+  </si>
+  <si>
+    <t>gehnakhandelwal17@gmail.com</t>
+  </si>
+  <si>
+    <t>9799914504</t>
+  </si>
+  <si>
+    <t>Kanoria PG Mahila Mahavidhyala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402,shree Shyam residency, Rani sati nagar,jaipur </t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:45:36 pm</t>
+  </si>
+  <si>
+    <t>Sharanyaa Upmanyu</t>
+  </si>
+  <si>
+    <t>2024btechaimlsharanyaa@poornima.edu.in</t>
+  </si>
+  <si>
+    <t>8962435250</t>
+  </si>
+  <si>
+    <t>Poornima University</t>
+  </si>
+  <si>
+    <t>Vidhani</t>
+  </si>
+  <si>
+    <t>Basketball (Girls)</t>
+  </si>
+  <si>
+    <t>9/3/2026, 10:18:33 pm</t>
+  </si>
+  <si>
+    <t>Ayushi Chouhan</t>
+  </si>
+  <si>
+    <t>chouhanayushi2711@gmail.com</t>
+  </si>
+  <si>
+    <t>9119341371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kanoria PG Mahila Mahavidyalaya </t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.42 Vinobha Marg, MI Road, Paanch Baati  C-Scheme </t>
+  </si>
+  <si>
+    <t>9/3/2026, 10:52:02 pm</t>
+  </si>
+  <si>
+    <t>Purvee Dudheria</t>
+  </si>
+  <si>
+    <t>purveedudheria@jklu.edu.in</t>
+  </si>
+  <si>
+    <t>9352221827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jk Lakshmipat University </t>
+  </si>
+  <si>
+    <t>Badminton (Singles) (Girls), Badminton (Doubles) (Girls), badminton-doubles-Girls</t>
+  </si>
+  <si>
+    <t>9/3/2026, 11:03:09 pm</t>
+  </si>
+  <si>
+    <t>Anvi Vashisht</t>
+  </si>
+  <si>
+    <t>anvivashisht@jklu.edu.in</t>
+  </si>
+  <si>
+    <t>+91 88755 13050</t>
+  </si>
+  <si>
+    <t>badminton-doubles-Girls</t>
+  </si>
+  <si>
+    <t>9/3/2026, 11:03:10 pm</t>
+  </si>
+  <si>
     <t>Event</t>
   </si>
   <si>
@@ -138,9 +387,21 @@
     <t>Team Name</t>
   </si>
   <si>
+    <t>Badminton (Doubles) (Girls)</t>
+  </si>
+  <si>
     <t>Individual</t>
   </si>
   <si>
+    <t>Leader</t>
+  </si>
+  <si>
+    <t>Purvee Dudheria's Team</t>
+  </si>
+  <si>
+    <t>Member</t>
+  </si>
+  <si>
     <t>Order ID</t>
   </si>
   <si>
@@ -265,6 +526,189 @@
   </si>
   <si>
     <t>25/2/2026, 10:29:50 am</t>
+  </si>
+  <si>
+    <t>order_536e61a35248</t>
+  </si>
+  <si>
+    <t>2/3/2026, 12:45:30 pm</t>
+  </si>
+  <si>
+    <t>order_425be306d7c6</t>
+  </si>
+  <si>
+    <t>7/3/2026, 3:28:25 pm</t>
+  </si>
+  <si>
+    <t>order_cdcab05c8aab</t>
+  </si>
+  <si>
+    <t>7/3/2026, 10:30:50 pm</t>
+  </si>
+  <si>
+    <t>order_d57985981984</t>
+  </si>
+  <si>
+    <t>7/3/2026, 10:34:23 pm</t>
+  </si>
+  <si>
+    <t>order_3089dca4b1c8</t>
+  </si>
+  <si>
+    <t>7/3/2026, 10:36:56 pm</t>
+  </si>
+  <si>
+    <t>order_219d28dc118d</t>
+  </si>
+  <si>
+    <t>9/3/2026, 12:59:41 pm</t>
+  </si>
+  <si>
+    <t>order_0d21ce3b7faa</t>
+  </si>
+  <si>
+    <t>9/3/2026, 5:30:47 pm</t>
+  </si>
+  <si>
+    <t>order_a7ce683b76c1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manant Srivastava </t>
+  </si>
+  <si>
+    <t>manant.sharad1012@gmail.com</t>
+  </si>
+  <si>
+    <t>9451021467</t>
+  </si>
+  <si>
+    <t>9/3/2026, 5:36:08 pm</t>
+  </si>
+  <si>
+    <t>order_856bb059d9c1</t>
+  </si>
+  <si>
+    <t>9/3/2026, 8:44:58 pm</t>
+  </si>
+  <si>
+    <t>order_2cfc3c179f82</t>
+  </si>
+  <si>
+    <t>9/3/2026, 8:49:37 pm</t>
+  </si>
+  <si>
+    <t>order_ef71f15f1f99</t>
+  </si>
+  <si>
+    <t>9/3/2026, 8:50:57 pm</t>
+  </si>
+  <si>
+    <t>order_53a27793a386</t>
+  </si>
+  <si>
+    <t>9/3/2026, 8:53:34 pm</t>
+  </si>
+  <si>
+    <t>order_8d866be928d0</t>
+  </si>
+  <si>
+    <t>9/3/2026, 8:55:42 pm</t>
+  </si>
+  <si>
+    <t>order_ab79aebd8dc7</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:24:33 pm</t>
+  </si>
+  <si>
+    <t>order_02e2cf888fa9</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:26:47 pm</t>
+  </si>
+  <si>
+    <t>order_b08f57b9d833</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:27:54 pm</t>
+  </si>
+  <si>
+    <t>order_8866e7342152</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:29:11 pm</t>
+  </si>
+  <si>
+    <t>order_c9a45082fc75</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:29:46 pm</t>
+  </si>
+  <si>
+    <t>order_ac0b3deb848d</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:30:47 pm</t>
+  </si>
+  <si>
+    <t>order_d612f65f8149</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:34:04 pm</t>
+  </si>
+  <si>
+    <t>order_ab3379803000</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:39:54 pm</t>
+  </si>
+  <si>
+    <t>order_098b86ab6d03</t>
+  </si>
+  <si>
+    <t>gunjanchoudhary18495@gmail.com</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:44:09 pm</t>
+  </si>
+  <si>
+    <t>order_0784d4a0289d</t>
+  </si>
+  <si>
+    <t>9/3/2026, 10:17:57 pm</t>
+  </si>
+  <si>
+    <t>order_8561c043e75b</t>
+  </si>
+  <si>
+    <t>9/3/2026, 10:19:04 pm</t>
+  </si>
+  <si>
+    <t>order_6699fa22c1ae</t>
+  </si>
+  <si>
+    <t>9/3/2026, 10:25:17 pm</t>
+  </si>
+  <si>
+    <t>order_dd9cca54b123</t>
+  </si>
+  <si>
+    <t>9/3/2026, 10:27:32 pm</t>
+  </si>
+  <si>
+    <t>order_e081def7a514</t>
+  </si>
+  <si>
+    <t>9/3/2026, 10:51:35 pm</t>
+  </si>
+  <si>
+    <t>order_09ed7d06d26f</t>
+  </si>
+  <si>
+    <t>Badminton (Singles) (Girls), Badminton (Doubles) (Girls)</t>
+  </si>
+  <si>
+    <t>9/3/2026, 11:01:47 pm</t>
   </si>
 </sst>
 </file>
@@ -669,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -682,11 +1126,11 @@
     <col min="8" max="8" width="35" customWidth="1"/>
     <col min="9" max="9" width="40" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="13" width="20" customWidth="1"/>
+    <col min="11" max="12" width="12" customWidth="1"/>
+    <col min="13" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -726,37 +1170,40 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
         <v>21</v>
@@ -767,37 +1214,40 @@
       <c r="M2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
         <v>21</v>
@@ -806,48 +1256,626 @@
         <v>22</v>
       </c>
       <c r="M3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4">
         <v>17</v>
       </c>
       <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
         <v>17</v>
       </c>
-      <c r="H4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="F5">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7">
         <v>20</v>
       </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4" t="s">
-        <v>37</v>
+      <c r="G7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" t="s">
+        <v>89</v>
+      </c>
+      <c r="I12" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>94</v>
+      </c>
+      <c r="H13" t="s">
+        <v>95</v>
+      </c>
+      <c r="I13" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s">
+        <v>100</v>
+      </c>
+      <c r="H14" t="s">
+        <v>101</v>
+      </c>
+      <c r="I14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I15" t="s">
+        <v>51</v>
+      </c>
+      <c r="J15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16">
+        <v>17</v>
+      </c>
+      <c r="G16" t="s">
+        <v>113</v>
+      </c>
+      <c r="H16" t="s">
+        <v>113</v>
+      </c>
+      <c r="I16" t="s">
+        <v>114</v>
+      </c>
+      <c r="J16" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" t="s">
+        <v>119</v>
+      </c>
+      <c r="J17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M17" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -859,7 +1887,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -871,14 +1899,15 @@
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>38</v>
+        <v>121</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -896,101 +1925,720 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="H2" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H3" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H6" t="s">
+        <v>125</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" t="s">
+        <v>113</v>
+      </c>
+      <c r="H7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I7" t="s">
+        <v>127</v>
+      </c>
+      <c r="J7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s">
+        <v>128</v>
+      </c>
+      <c r="I8" t="s">
+        <v>127</v>
+      </c>
+      <c r="J8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" t="s">
+        <v>100</v>
+      </c>
+      <c r="H11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" t="s">
+        <v>125</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D13" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E13" t="s">
         <v>27</v>
       </c>
-      <c r="G4" t="s">
+      <c r="F13" t="s">
         <v>28</v>
       </c>
-      <c r="H4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
+        <v>125</v>
+      </c>
+      <c r="I13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" t="s">
+        <v>125</v>
+      </c>
+      <c r="I14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" t="s">
+        <v>125</v>
+      </c>
+      <c r="I15" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" t="s">
+        <v>125</v>
+      </c>
+      <c r="I17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" t="s">
+        <v>82</v>
+      </c>
+      <c r="H18" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" t="s">
+        <v>125</v>
+      </c>
+      <c r="I19" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" t="s">
+        <v>125</v>
+      </c>
+      <c r="I20" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" t="s">
+        <v>107</v>
+      </c>
+      <c r="H21" t="s">
+        <v>125</v>
+      </c>
+      <c r="I21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -998,7 +2646,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1018,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
@@ -1030,19 +2678,19 @@
         <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1050,31 +2698,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2">
         <v>150</v>
       </c>
       <c r="H2" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1082,31 +2730,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="G3">
         <v>251</v>
       </c>
       <c r="H3" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1114,31 +2762,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4">
         <v>150</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>145</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1146,31 +2794,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>147</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>150</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>151</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>145</v>
       </c>
       <c r="I5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J5" t="s">
-        <v>65</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1178,31 +2826,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>58</v>
+        <v>145</v>
       </c>
       <c r="I6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J6" t="s">
-        <v>67</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -1210,31 +2858,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>156</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>157</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>158</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>159</v>
       </c>
       <c r="G7">
         <v>800</v>
       </c>
       <c r="H7" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="I7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J7" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1242,31 +2890,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>156</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>157</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>158</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="G8">
         <v>3152</v>
       </c>
       <c r="H8" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="I8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J8" t="s">
-        <v>76</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1274,31 +2922,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G9">
         <v>250</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>145</v>
       </c>
       <c r="I9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J9" t="s">
-        <v>78</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1306,31 +2954,927 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>168</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10">
         <v>150</v>
       </c>
       <c r="H10" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="I10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" t="s">
-        <v>83</v>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E11" t="s">
+        <v>150</v>
+      </c>
+      <c r="F11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>136</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12">
+        <v>250</v>
+      </c>
+      <c r="H12" t="s">
+        <v>145</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>145</v>
+      </c>
+      <c r="I13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>136</v>
+      </c>
+      <c r="I14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>179</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>136</v>
+      </c>
+      <c r="I15" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>181</v>
+      </c>
+      <c r="C16" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" t="s">
+        <v>149</v>
+      </c>
+      <c r="E16" t="s">
+        <v>150</v>
+      </c>
+      <c r="F16" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16">
+        <v>250</v>
+      </c>
+      <c r="H16" t="s">
+        <v>136</v>
+      </c>
+      <c r="I16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17" t="s">
+        <v>145</v>
+      </c>
+      <c r="I17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" t="s">
+        <v>186</v>
+      </c>
+      <c r="D18" t="s">
+        <v>187</v>
+      </c>
+      <c r="E18" t="s">
+        <v>188</v>
+      </c>
+      <c r="F18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18">
+        <v>250</v>
+      </c>
+      <c r="H18" t="s">
+        <v>136</v>
+      </c>
+      <c r="I18" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>136</v>
+      </c>
+      <c r="I19" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C20" t="s">
+        <v>148</v>
+      </c>
+      <c r="D20" t="s">
+        <v>149</v>
+      </c>
+      <c r="E20" t="s">
+        <v>150</v>
+      </c>
+      <c r="F20" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>136</v>
+      </c>
+      <c r="I20" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>194</v>
+      </c>
+      <c r="C21" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" t="s">
+        <v>149</v>
+      </c>
+      <c r="E21" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>145</v>
+      </c>
+      <c r="I21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" t="s">
+        <v>65</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>136</v>
+      </c>
+      <c r="I22" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>198</v>
+      </c>
+      <c r="C23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>145</v>
+      </c>
+      <c r="I23" t="s">
+        <v>23</v>
+      </c>
+      <c r="J23" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>200</v>
+      </c>
+      <c r="C24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>136</v>
+      </c>
+      <c r="I24" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>202</v>
+      </c>
+      <c r="C25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" t="s">
+        <v>145</v>
+      </c>
+      <c r="I25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>204</v>
+      </c>
+      <c r="C26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
+        <v>136</v>
+      </c>
+      <c r="I26" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>206</v>
+      </c>
+      <c r="C27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" t="s">
+        <v>75</v>
+      </c>
+      <c r="F27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="s">
+        <v>145</v>
+      </c>
+      <c r="I27" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" t="s">
+        <v>81</v>
+      </c>
+      <c r="F28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28" t="s">
+        <v>145</v>
+      </c>
+      <c r="I28" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>210</v>
+      </c>
+      <c r="C29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" t="s">
+        <v>51</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29" t="s">
+        <v>145</v>
+      </c>
+      <c r="I29" t="s">
+        <v>23</v>
+      </c>
+      <c r="J29" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>212</v>
+      </c>
+      <c r="C30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" t="s">
+        <v>51</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30" t="s">
+        <v>136</v>
+      </c>
+      <c r="I30" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>214</v>
+      </c>
+      <c r="C31" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" t="s">
+        <v>92</v>
+      </c>
+      <c r="E31" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" t="s">
+        <v>51</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31" t="s">
+        <v>145</v>
+      </c>
+      <c r="I31" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>216</v>
+      </c>
+      <c r="C32" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" t="s">
+        <v>217</v>
+      </c>
+      <c r="E32" t="s">
+        <v>69</v>
+      </c>
+      <c r="F32" t="s">
+        <v>51</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32" t="s">
+        <v>136</v>
+      </c>
+      <c r="I32" t="s">
+        <v>23</v>
+      </c>
+      <c r="J32" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>219</v>
+      </c>
+      <c r="C33" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33" t="s">
+        <v>99</v>
+      </c>
+      <c r="F33" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
+        <v>145</v>
+      </c>
+      <c r="I33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>221</v>
+      </c>
+      <c r="C34" t="s">
+        <v>97</v>
+      </c>
+      <c r="D34" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" t="s">
+        <v>99</v>
+      </c>
+      <c r="F34" t="s">
+        <v>102</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34" t="s">
+        <v>136</v>
+      </c>
+      <c r="I34" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>223</v>
+      </c>
+      <c r="C35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" t="s">
+        <v>98</v>
+      </c>
+      <c r="E35" t="s">
+        <v>99</v>
+      </c>
+      <c r="F35" t="s">
+        <v>102</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35" t="s">
+        <v>136</v>
+      </c>
+      <c r="I35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>225</v>
+      </c>
+      <c r="C36" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36" t="s">
+        <v>99</v>
+      </c>
+      <c r="F36" t="s">
+        <v>102</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36" t="s">
+        <v>145</v>
+      </c>
+      <c r="I36" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>227</v>
+      </c>
+      <c r="C37" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" t="s">
+        <v>105</v>
+      </c>
+      <c r="E37" t="s">
+        <v>106</v>
+      </c>
+      <c r="F37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37" t="s">
+        <v>145</v>
+      </c>
+      <c r="I37" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>229</v>
+      </c>
+      <c r="C38" t="s">
+        <v>110</v>
+      </c>
+      <c r="D38" t="s">
+        <v>111</v>
+      </c>
+      <c r="E38" t="s">
+        <v>112</v>
+      </c>
+      <c r="F38" t="s">
+        <v>230</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+      <c r="H38" t="s">
+        <v>145</v>
+      </c>
+      <c r="I38" t="s">
+        <v>23</v>
+      </c>
+      <c r="J38" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/registrations_export.xlsx
+++ b/registrations_export.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="311">
   <si>
     <t>S.No</t>
   </si>
@@ -39,7 +39,19 @@
     <t>Address</t>
   </si>
   <si>
-    <t>Events Registered</t>
+    <t>Referral Code</t>
+  </si>
+  <si>
+    <t>University ID Card</t>
+  </si>
+  <si>
+    <t>Event 1</t>
+  </si>
+  <si>
+    <t>Event 2</t>
+  </si>
+  <si>
+    <t>Event 3</t>
   </si>
   <si>
     <t>Email Verified</t>
@@ -75,6 +87,12 @@
     <t>Vaishali Nagar, Jaipur</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>2025btech025</t>
+  </si>
+  <si>
     <t>Chess (Boys)</t>
   </si>
   <si>
@@ -84,9 +102,6 @@
     <t>No</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>23/2/2026, 9:50:42 am</t>
   </si>
   <si>
@@ -108,6 +123,9 @@
     <t>Rashmi, Chittorgarh</t>
   </si>
   <si>
+    <t>U-0657</t>
+  </si>
+  <si>
     <t>Football (5v5) (Girls)</t>
   </si>
   <si>
@@ -126,6 +144,9 @@
     <t>4-9-94 attapur, Rajendra nagar PO: Hyderguda, DIST: k. v. Rangareddy, Telangana 500048</t>
   </si>
   <si>
+    <t>2025BTech176</t>
+  </si>
+  <si>
     <t>Basketball (Boys)</t>
   </si>
   <si>
@@ -147,6 +168,9 @@
     <t>302026, jaipur</t>
   </si>
   <si>
+    <t>mohitsuwalka@jklu.edu.in</t>
+  </si>
+  <si>
     <t>Badminton (Singles) (Boys)</t>
   </si>
   <si>
@@ -168,6 +192,9 @@
     <t>58 vrindavan colony jhotwara jaipur, Rajasthan</t>
   </si>
   <si>
+    <t>2024/2338</t>
+  </si>
+  <si>
     <t>Volleyball (Girls)</t>
   </si>
   <si>
@@ -189,384 +216,513 @@
     <t xml:space="preserve">Himalayan  Hospital  jollygrant  dheradun  Near sbi Atm Jolly Grant Dehradun </t>
   </si>
   <si>
+    <t>DD241103301154</t>
+  </si>
+  <si>
+    <t>Basketball (Girls)</t>
+  </si>
+  <si>
+    <t>Badminton (Singles) (Girls)</t>
+  </si>
+  <si>
+    <t>9/3/2026, 5:32:41 pm</t>
+  </si>
+  <si>
+    <t>Ruchika Mathur</t>
+  </si>
+  <si>
+    <t>ruchimathurcute2007@gmail.com</t>
+  </si>
+  <si>
+    <t>08619871879</t>
+  </si>
+  <si>
+    <t>Kanoria PG Mahila Mahavidyalaya</t>
+  </si>
+  <si>
+    <t>Jawahar Lal Nehru Marg, Near Gandhi Circle - Kanodiya Bus Stop, Bapu Nagar</t>
+  </si>
+  <si>
+    <t>2025/0313</t>
+  </si>
+  <si>
+    <t>9/3/2026, 8:57:36 pm</t>
+  </si>
+  <si>
+    <t>Gunjan Choudhary</t>
+  </si>
+  <si>
+    <t>gunjan2003.choudhary@gmail.com</t>
+  </si>
+  <si>
+    <t>8278671820</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kanoria pg mahila Mahavidyalaya </t>
+  </si>
+  <si>
+    <t>Kanoria Pg Mahila Mahavidyalaya Main Campus, Kanoria Pg Mahila Mahavidyalaya, Jawahar Lal Nehru Marg, Bapu Nagar, Jaipur, Rajasthan 302015</t>
+  </si>
+  <si>
+    <t>2025/2388</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:27:20 pm</t>
+  </si>
+  <si>
+    <t>Sakshi Sharma</t>
+  </si>
+  <si>
+    <t>sakshisharmasakshi707@gmail.com</t>
+  </si>
+  <si>
+    <t>7850079584</t>
+  </si>
+  <si>
+    <t>Kanoria P G Mahila Mahavidyalaya</t>
+  </si>
+  <si>
+    <t>Jawahar Lal Nehru marg,  near Gandhi circle -Kanoria Bus stop, Bapu nagar-302015</t>
+  </si>
+  <si>
+    <t>2025/1387</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:29:43 pm</t>
+  </si>
+  <si>
+    <t>Chitman kaur</t>
+  </si>
+  <si>
+    <t>kaurchitman1@gmail.com</t>
+  </si>
+  <si>
+    <t>9799208648</t>
+  </si>
+  <si>
+    <t>Kanoria pg mahila mahavidayala</t>
+  </si>
+  <si>
+    <t>1200, barkat nagar kissan marg near Axis bank, jaipur</t>
+  </si>
+  <si>
+    <t>2025/1178</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:30:24 pm</t>
+  </si>
+  <si>
+    <t>Surbhi Sharma</t>
+  </si>
+  <si>
+    <t>surbhisharma22996@gmail.com</t>
+  </si>
+  <si>
+    <t>9079650130</t>
+  </si>
+  <si>
+    <t>Kanoria pg mahila mahavidyalay jaipur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175 parshvanath negar near airport sanganer jaipur </t>
+  </si>
+  <si>
+    <t>2025/0080</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:32:23 pm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gehna Khandelwal </t>
+  </si>
+  <si>
+    <t>gehnakhandelwal17@gmail.com</t>
+  </si>
+  <si>
+    <t>9799914504</t>
+  </si>
+  <si>
+    <t>Kanoria PG Mahila Mahavidhyala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402,shree Shyam residency, Rani sati nagar,jaipur </t>
+  </si>
+  <si>
+    <t>2025/1224</t>
+  </si>
+  <si>
+    <t>9/3/2026, 9:45:36 pm</t>
+  </si>
+  <si>
+    <t>Sharanyaa Upmanyu</t>
+  </si>
+  <si>
+    <t>2024btechaimlsharanyaa@poornima.edu.in</t>
+  </si>
+  <si>
+    <t>8962435250</t>
+  </si>
+  <si>
+    <t>Poornima University</t>
+  </si>
+  <si>
+    <t>Vidhani</t>
+  </si>
+  <si>
+    <t>2024/19438</t>
+  </si>
+  <si>
+    <t>9/3/2026, 10:18:33 pm</t>
+  </si>
+  <si>
+    <t>Ayushi Chouhan</t>
+  </si>
+  <si>
+    <t>chouhanayushi2711@gmail.com</t>
+  </si>
+  <si>
+    <t>9119341371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kanoria PG Mahila Mahavidyalaya </t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.42 Vinobha Marg, MI Road, Paanch Baati  C-Scheme </t>
+  </si>
+  <si>
+    <t>2022/2016</t>
+  </si>
+  <si>
+    <t>9/3/2026, 10:52:02 pm</t>
+  </si>
+  <si>
+    <t>Purvee Dudheria</t>
+  </si>
+  <si>
+    <t>purveedudheria@jklu.edu.in</t>
+  </si>
+  <si>
+    <t>9352221827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jk Lakshmipat University </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2025BBA090</t>
+  </si>
+  <si>
+    <t>Badminton (Doubles) (Girls)</t>
+  </si>
+  <si>
+    <t>badminton-doubles-Girls</t>
+  </si>
+  <si>
+    <t>9/3/2026, 11:03:09 pm</t>
+  </si>
+  <si>
+    <t>Anvi Vashisht</t>
+  </si>
+  <si>
+    <t>anvivashisht@jklu.edu.in</t>
+  </si>
+  <si>
+    <t>+91 88755 13050</t>
+  </si>
+  <si>
+    <t>9/3/2026, 11:03:10 pm</t>
+  </si>
+  <si>
+    <t>Kanchan kumari</t>
+  </si>
+  <si>
+    <t>kanchankumari7878836@gmail.com</t>
+  </si>
+  <si>
+    <t>7878836380</t>
+  </si>
+  <si>
+    <t>Gandhi circle,jln marg</t>
+  </si>
+  <si>
+    <t>2025/0256</t>
+  </si>
+  <si>
+    <t>10/3/2026, 6:53:21 am</t>
+  </si>
+  <si>
+    <t>Archita Bhargava</t>
+  </si>
+  <si>
+    <t>architabhargava7@gmail.com</t>
+  </si>
+  <si>
+    <t>6377284958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jk Lakshmipat university </t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-14 bhagirath nagar arjun Nagar gopalpura bypass road Jaipur </t>
+  </si>
+  <si>
+    <t>2022btech122</t>
+  </si>
+  <si>
+    <t>Badminton (Mixed) (Girls)</t>
+  </si>
+  <si>
+    <t>10/3/2026, 11:56:49 am</t>
+  </si>
+  <si>
+    <t>architabhargava@jklu.edu.in</t>
+  </si>
+  <si>
+    <t>10/3/2026, 11:56:50 am</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anvi vashist </t>
+  </si>
+  <si>
+    <t>anvivashist@jklu.edu.in</t>
+  </si>
+  <si>
+    <t>8875513050</t>
+  </si>
+  <si>
+    <t>Ashok kumar</t>
+  </si>
+  <si>
+    <t>nitinsanwar97@gmail.com</t>
+  </si>
+  <si>
+    <t>7428864638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jc Bose university of science and technology YMCA faridabad </t>
+  </si>
+  <si>
+    <t>Faridabad sec 6</t>
+  </si>
+  <si>
+    <t>25021236002</t>
+  </si>
+  <si>
+    <t>Kabaddi (Boys)</t>
+  </si>
+  <si>
+    <t>kabaddi-Boys</t>
+  </si>
+  <si>
+    <t>11/3/2026, 7:32:59 pm</t>
+  </si>
+  <si>
+    <t>Mohit</t>
+  </si>
+  <si>
+    <t>mohitrawat97@gmail.com</t>
+  </si>
+  <si>
+    <t>9891202902</t>
+  </si>
+  <si>
+    <t>11/3/2026, 7:33:00 pm</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Team Name</t>
+  </si>
+  <si>
+    <t>Individual</t>
+  </si>
+  <si>
+    <t>Leader</t>
+  </si>
+  <si>
+    <t>Purvee Dudheria's Team</t>
+  </si>
+  <si>
+    <t>Member</t>
+  </si>
+  <si>
+    <t>Archita Bhargava's Team</t>
+  </si>
+  <si>
+    <t>Ashok kumar's Team</t>
+  </si>
+  <si>
+    <t>Order ID</t>
+  </si>
+  <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Amount (₹)</t>
+  </si>
+  <si>
+    <t>Payment Status</t>
+  </si>
+  <si>
+    <t>Transaction ID</t>
+  </si>
+  <si>
+    <t>Payment Date</t>
+  </si>
+  <si>
+    <t>order_13c528dc980e</t>
+  </si>
+  <si>
+    <t>pending</t>
+  </si>
+  <si>
+    <t>22/2/2026, 6:17:12 pm</t>
+  </si>
+  <si>
+    <t>order_dc9a40e23a64</t>
+  </si>
+  <si>
+    <t>shlok chaturvedi</t>
+  </si>
+  <si>
+    <t>shlokchaturvedi@jklu.edu.in</t>
+  </si>
+  <si>
+    <t>07737257861</t>
+  </si>
+  <si>
+    <t>Football (5v5) (Girls), Basketball (Boys)</t>
+  </si>
+  <si>
+    <t>22/2/2026, 9:12:47 pm</t>
+  </si>
+  <si>
+    <t>order_b40680149159</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>23/2/2026, 9:46:45 am</t>
+  </si>
+  <si>
+    <t>order_95a81276d2c1</t>
+  </si>
+  <si>
+    <t>Yash Bansal</t>
+  </si>
+  <si>
+    <t>yashbansal531@gmail.com</t>
+  </si>
+  <si>
+    <t>8619011601</t>
+  </si>
+  <si>
+    <t>Chess (Girls)</t>
+  </si>
+  <si>
+    <t>23/2/2026, 4:26:52 pm</t>
+  </si>
+  <si>
+    <t>order_1538dde5a355</t>
+  </si>
+  <si>
+    <t>23/2/2026, 5:21:57 pm</t>
+  </si>
+  <si>
+    <t>order_bfda25f8550d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N n </t>
+  </si>
+  <si>
+    <t>abc@gmail.com</t>
+  </si>
+  <si>
+    <t>9876543210</t>
+  </si>
+  <si>
+    <t>Chess (Boys), Badminton (Singles) (Boys), Leather Cricket (Boys)</t>
+  </si>
+  <si>
+    <t>24/2/2026, 12:21:30 pm</t>
+  </si>
+  <si>
+    <t>order_5605d9607044</t>
+  </si>
+  <si>
+    <t>Chess (Boys), Badminton (Singles) (Boys), Leather Cricket (Boys), Badminton (Mixed) (Boys), Football (7v7) (Boys), Football (5v5) (Girls), Basketball (Boys), Badminton (Doubles) (Boys), Badminton (Doubles) (Girls), Box Cricket (Boys)</t>
+  </si>
+  <si>
+    <t>24/2/2026, 12:28:01 pm</t>
+  </si>
+  <si>
+    <t>order_756d4e939ebd</t>
+  </si>
+  <si>
+    <t>24/2/2026, 8:20:46 pm</t>
+  </si>
+  <si>
+    <t>order_c12e424ce3fb</t>
+  </si>
+  <si>
+    <t>dipanshu bansal</t>
+  </si>
+  <si>
+    <t>sg169947@gmail.com</t>
+  </si>
+  <si>
+    <t>07378119932</t>
+  </si>
+  <si>
+    <t>25/2/2026, 10:29:50 am</t>
+  </si>
+  <si>
+    <t>order_536e61a35248</t>
+  </si>
+  <si>
+    <t>2/3/2026, 12:45:30 pm</t>
+  </si>
+  <si>
+    <t>order_425be306d7c6</t>
+  </si>
+  <si>
+    <t>7/3/2026, 3:28:25 pm</t>
+  </si>
+  <si>
+    <t>order_cdcab05c8aab</t>
+  </si>
+  <si>
+    <t>7/3/2026, 10:30:50 pm</t>
+  </si>
+  <si>
+    <t>order_d57985981984</t>
+  </si>
+  <si>
+    <t>7/3/2026, 10:34:23 pm</t>
+  </si>
+  <si>
+    <t>order_3089dca4b1c8</t>
+  </si>
+  <si>
+    <t>7/3/2026, 10:36:56 pm</t>
+  </si>
+  <si>
+    <t>order_219d28dc118d</t>
+  </si>
+  <si>
+    <t>9/3/2026, 12:59:41 pm</t>
+  </si>
+  <si>
+    <t>order_0d21ce3b7faa</t>
+  </si>
+  <si>
     <t>Basketball (Girls), Volleyball (Girls), Badminton (Singles) (Girls)</t>
   </si>
   <si>
-    <t>9/3/2026, 5:32:41 pm</t>
-  </si>
-  <si>
-    <t>Ruchika Mathur</t>
-  </si>
-  <si>
-    <t>ruchimathurcute2007@gmail.com</t>
-  </si>
-  <si>
-    <t>08619871879</t>
-  </si>
-  <si>
-    <t>Kanoria PG Mahila Mahavidyalaya</t>
-  </si>
-  <si>
-    <t>Jawahar Lal Nehru Marg, Near Gandhi Circle - Kanodiya Bus Stop, Bapu Nagar</t>
-  </si>
-  <si>
-    <t>Badminton (Singles) (Girls)</t>
-  </si>
-  <si>
-    <t>9/3/2026, 8:57:36 pm</t>
-  </si>
-  <si>
-    <t>Gunjan Choudhary</t>
-  </si>
-  <si>
-    <t>gunjan2003.choudhary@gmail.com</t>
-  </si>
-  <si>
-    <t>8278671820</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kanoria pg mahila Mahavidyalaya </t>
-  </si>
-  <si>
-    <t>Kanoria Pg Mahila Mahavidyalaya Main Campus, Kanoria Pg Mahila Mahavidyalaya, Jawahar Lal Nehru Marg, Bapu Nagar, Jaipur, Rajasthan 302015</t>
-  </si>
-  <si>
-    <t>9/3/2026, 9:27:20 pm</t>
-  </si>
-  <si>
-    <t>Sakshi Sharma</t>
-  </si>
-  <si>
-    <t>sakshisharmasakshi707@gmail.com</t>
-  </si>
-  <si>
-    <t>7850079584</t>
-  </si>
-  <si>
-    <t>Kanoria P G Mahila Mahavidyalaya</t>
-  </si>
-  <si>
-    <t>Jawahar Lal Nehru marg,  near Gandhi circle -Kanoria Bus stop, Bapu nagar-302015</t>
-  </si>
-  <si>
-    <t>9/3/2026, 9:29:43 pm</t>
-  </si>
-  <si>
-    <t>Chitman kaur</t>
-  </si>
-  <si>
-    <t>kaurchitman1@gmail.com</t>
-  </si>
-  <si>
-    <t>9799208648</t>
-  </si>
-  <si>
-    <t>Kanoria pg mahila mahavidayala</t>
-  </si>
-  <si>
-    <t>1200, barkat nagar kissan marg near Axis bank, jaipur</t>
-  </si>
-  <si>
-    <t>9/3/2026, 9:30:24 pm</t>
-  </si>
-  <si>
-    <t>Surbhi Sharma</t>
-  </si>
-  <si>
-    <t>surbhisharma22996@gmail.com</t>
-  </si>
-  <si>
-    <t>9079650130</t>
-  </si>
-  <si>
-    <t>Kanoria pg mahila mahavidyalay jaipur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175 parshvanath negar near airport sanganer jaipur </t>
-  </si>
-  <si>
-    <t>9/3/2026, 9:32:23 pm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gehna Khandelwal </t>
-  </si>
-  <si>
-    <t>gehnakhandelwal17@gmail.com</t>
-  </si>
-  <si>
-    <t>9799914504</t>
-  </si>
-  <si>
-    <t>Kanoria PG Mahila Mahavidhyala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402,shree Shyam residency, Rani sati nagar,jaipur </t>
-  </si>
-  <si>
-    <t>9/3/2026, 9:45:36 pm</t>
-  </si>
-  <si>
-    <t>Sharanyaa Upmanyu</t>
-  </si>
-  <si>
-    <t>2024btechaimlsharanyaa@poornima.edu.in</t>
-  </si>
-  <si>
-    <t>8962435250</t>
-  </si>
-  <si>
-    <t>Poornima University</t>
-  </si>
-  <si>
-    <t>Vidhani</t>
-  </si>
-  <si>
-    <t>Basketball (Girls)</t>
-  </si>
-  <si>
-    <t>9/3/2026, 10:18:33 pm</t>
-  </si>
-  <si>
-    <t>Ayushi Chouhan</t>
-  </si>
-  <si>
-    <t>chouhanayushi2711@gmail.com</t>
-  </si>
-  <si>
-    <t>9119341371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kanoria PG Mahila Mahavidyalaya </t>
-  </si>
-  <si>
-    <t xml:space="preserve">P.42 Vinobha Marg, MI Road, Paanch Baati  C-Scheme </t>
-  </si>
-  <si>
-    <t>9/3/2026, 10:52:02 pm</t>
-  </si>
-  <si>
-    <t>Purvee Dudheria</t>
-  </si>
-  <si>
-    <t>purveedudheria@jklu.edu.in</t>
-  </si>
-  <si>
-    <t>9352221827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jk Lakshmipat University </t>
-  </si>
-  <si>
-    <t>Badminton (Singles) (Girls), Badminton (Doubles) (Girls), badminton-doubles-Girls</t>
-  </si>
-  <si>
-    <t>9/3/2026, 11:03:09 pm</t>
-  </si>
-  <si>
-    <t>Anvi Vashisht</t>
-  </si>
-  <si>
-    <t>anvivashisht@jklu.edu.in</t>
-  </si>
-  <si>
-    <t>+91 88755 13050</t>
-  </si>
-  <si>
-    <t>badminton-doubles-Girls</t>
-  </si>
-  <si>
-    <t>9/3/2026, 11:03:10 pm</t>
-  </si>
-  <si>
-    <t>Event</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>Team Name</t>
-  </si>
-  <si>
-    <t>Badminton (Doubles) (Girls)</t>
-  </si>
-  <si>
-    <t>Individual</t>
-  </si>
-  <si>
-    <t>Leader</t>
-  </si>
-  <si>
-    <t>Purvee Dudheria's Team</t>
-  </si>
-  <si>
-    <t>Member</t>
-  </si>
-  <si>
-    <t>Order ID</t>
-  </si>
-  <si>
-    <t>Events</t>
-  </si>
-  <si>
-    <t>Amount (₹)</t>
-  </si>
-  <si>
-    <t>Payment Status</t>
-  </si>
-  <si>
-    <t>Transaction ID</t>
-  </si>
-  <si>
-    <t>Payment Date</t>
-  </si>
-  <si>
-    <t>order_13c528dc980e</t>
-  </si>
-  <si>
-    <t>pending</t>
-  </si>
-  <si>
-    <t>22/2/2026, 6:17:12 pm</t>
-  </si>
-  <si>
-    <t>order_dc9a40e23a64</t>
-  </si>
-  <si>
-    <t>shlok chaturvedi</t>
-  </si>
-  <si>
-    <t>shlokchaturvedi@jklu.edu.in</t>
-  </si>
-  <si>
-    <t>07737257861</t>
-  </si>
-  <si>
-    <t>Football (5v5) (Girls), Basketball (Boys)</t>
-  </si>
-  <si>
-    <t>22/2/2026, 9:12:47 pm</t>
-  </si>
-  <si>
-    <t>order_b40680149159</t>
-  </si>
-  <si>
-    <t>completed</t>
-  </si>
-  <si>
-    <t>23/2/2026, 9:46:45 am</t>
-  </si>
-  <si>
-    <t>order_95a81276d2c1</t>
-  </si>
-  <si>
-    <t>Yash Bansal</t>
-  </si>
-  <si>
-    <t>yashbansal531@gmail.com</t>
-  </si>
-  <si>
-    <t>8619011601</t>
-  </si>
-  <si>
-    <t>Chess (Girls)</t>
-  </si>
-  <si>
-    <t>23/2/2026, 4:26:52 pm</t>
-  </si>
-  <si>
-    <t>order_1538dde5a355</t>
-  </si>
-  <si>
-    <t>23/2/2026, 5:21:57 pm</t>
-  </si>
-  <si>
-    <t>order_bfda25f8550d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N n </t>
-  </si>
-  <si>
-    <t>abc@gmail.com</t>
-  </si>
-  <si>
-    <t>9876543210</t>
-  </si>
-  <si>
-    <t>Chess (Boys), Badminton (Singles) (Boys), Leather Cricket (Boys)</t>
-  </si>
-  <si>
-    <t>24/2/2026, 12:21:30 pm</t>
-  </si>
-  <si>
-    <t>order_5605d9607044</t>
-  </si>
-  <si>
-    <t>Chess (Boys), Badminton (Singles) (Boys), Leather Cricket (Boys), Badminton (Mixed) (Boys), Football (7v7) (Boys), Football (5v5) (Girls), Basketball (Boys), Badminton (Doubles) (Boys), Badminton (Doubles) (Girls), Box Cricket (Boys)</t>
-  </si>
-  <si>
-    <t>24/2/2026, 12:28:01 pm</t>
-  </si>
-  <si>
-    <t>order_756d4e939ebd</t>
-  </si>
-  <si>
-    <t>24/2/2026, 8:20:46 pm</t>
-  </si>
-  <si>
-    <t>order_c12e424ce3fb</t>
-  </si>
-  <si>
-    <t>dipanshu bansal</t>
-  </si>
-  <si>
-    <t>sg169947@gmail.com</t>
-  </si>
-  <si>
-    <t>07378119932</t>
-  </si>
-  <si>
-    <t>25/2/2026, 10:29:50 am</t>
-  </si>
-  <si>
-    <t>order_536e61a35248</t>
-  </si>
-  <si>
-    <t>2/3/2026, 12:45:30 pm</t>
-  </si>
-  <si>
-    <t>order_425be306d7c6</t>
-  </si>
-  <si>
-    <t>7/3/2026, 3:28:25 pm</t>
-  </si>
-  <si>
-    <t>order_cdcab05c8aab</t>
-  </si>
-  <si>
-    <t>7/3/2026, 10:30:50 pm</t>
-  </si>
-  <si>
-    <t>order_d57985981984</t>
-  </si>
-  <si>
-    <t>7/3/2026, 10:34:23 pm</t>
-  </si>
-  <si>
-    <t>order_3089dca4b1c8</t>
-  </si>
-  <si>
-    <t>7/3/2026, 10:36:56 pm</t>
-  </si>
-  <si>
-    <t>order_219d28dc118d</t>
-  </si>
-  <si>
-    <t>9/3/2026, 12:59:41 pm</t>
-  </si>
-  <si>
-    <t>order_0d21ce3b7faa</t>
-  </si>
-  <si>
     <t>9/3/2026, 5:30:47 pm</t>
   </si>
   <si>
@@ -709,6 +865,87 @@
   </si>
   <si>
     <t>9/3/2026, 11:01:47 pm</t>
+  </si>
+  <si>
+    <t>order_97c4053806b6</t>
+  </si>
+  <si>
+    <t>10/3/2026, 6:26:07 am</t>
+  </si>
+  <si>
+    <t>order_17860f32c342</t>
+  </si>
+  <si>
+    <t>10/3/2026, 6:28:29 am</t>
+  </si>
+  <si>
+    <t>order_a54c2583b043</t>
+  </si>
+  <si>
+    <t>10/3/2026, 6:52:19 am</t>
+  </si>
+  <si>
+    <t>order_ca86a6184023</t>
+  </si>
+  <si>
+    <t>Badminton (Mixed) (Girls), Badminton (Doubles) (Girls), Badminton (Singles) (Girls)</t>
+  </si>
+  <si>
+    <t>10/3/2026, 11:56:14 am</t>
+  </si>
+  <si>
+    <t>order_b10e4b2a0f76</t>
+  </si>
+  <si>
+    <t>hsjus suis</t>
+  </si>
+  <si>
+    <t>dhej@dyd.com</t>
+  </si>
+  <si>
+    <t>9464616184</t>
+  </si>
+  <si>
+    <t>Badminton (Singles) (Boys), Badminton (Doubles) (Boys)</t>
+  </si>
+  <si>
+    <t>10/3/2026, 1:00:50 pm</t>
+  </si>
+  <si>
+    <t>order_4a51b0517442</t>
+  </si>
+  <si>
+    <t>10/3/2026, 2:25:25 pm</t>
+  </si>
+  <si>
+    <t>order_bff1882ab30b</t>
+  </si>
+  <si>
+    <t>10/3/2026, 4:23:11 pm</t>
+  </si>
+  <si>
+    <t>order_f62a05f6ca23</t>
+  </si>
+  <si>
+    <t>10/3/2026, 4:36:46 pm</t>
+  </si>
+  <si>
+    <t>order_f4927230f8ff</t>
+  </si>
+  <si>
+    <t>10/3/2026, 6:59:25 pm</t>
+  </si>
+  <si>
+    <t>order_7796288ab1e2</t>
+  </si>
+  <si>
+    <t>11/3/2026, 6:41:59 am</t>
+  </si>
+  <si>
+    <t>order_3edf6dac7893</t>
+  </si>
+  <si>
+    <t>11/3/2026, 7:32:19 pm</t>
   </si>
 </sst>
 </file>
@@ -1113,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1124,13 +1361,15 @@
     <col min="6" max="6" width="6" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="35" customWidth="1"/>
-    <col min="9" max="9" width="40" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="12" width="12" customWidth="1"/>
-    <col min="13" max="14" width="20" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="13" width="25" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="16" width="12" customWidth="1"/>
+    <col min="17" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1173,713 +1412,1253 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="J4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="L4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F5">
         <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I5" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="L5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>24</v>
+      </c>
+      <c r="R5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I6" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="K6" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="L6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>24</v>
+      </c>
+      <c r="R6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H7" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="K7" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L7" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="M7" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="N7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O7" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F8">
         <v>18</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="H8" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="I8" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="J8" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="K8" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="L8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O8" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>24</v>
+      </c>
+      <c r="R8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F9">
         <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="J9" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="K9" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O9" t="s">
+        <v>27</v>
+      </c>
+      <c r="P9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>24</v>
+      </c>
+      <c r="R9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F10">
         <v>19</v>
       </c>
       <c r="G10" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I10" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="J10" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K10" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="L10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O10" t="s">
+        <v>27</v>
+      </c>
+      <c r="P10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>24</v>
+      </c>
+      <c r="R10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F11">
         <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H11" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I11" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="J11" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="K11" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="L11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O11" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>24</v>
+      </c>
+      <c r="R11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F12">
         <v>19</v>
       </c>
       <c r="G12" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H12" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="I12" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="J12" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="K12" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="L12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O12" t="s">
+        <v>27</v>
+      </c>
+      <c r="P12" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>24</v>
+      </c>
+      <c r="R12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F13">
         <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="H13" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="I13" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="J13" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="K13" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="L13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N13" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O13" t="s">
+        <v>27</v>
+      </c>
+      <c r="P13" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>24</v>
+      </c>
+      <c r="R13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F14">
         <v>19</v>
       </c>
       <c r="G14" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="H14" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="I14" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="J14" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="K14" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N14" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O14" t="s">
+        <v>27</v>
+      </c>
+      <c r="P14" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>24</v>
+      </c>
+      <c r="R14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F15">
         <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="H15" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="I15" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="J15" t="s">
-        <v>21</v>
+        <v>125</v>
       </c>
       <c r="K15" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="L15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N15" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O15" t="s">
+        <v>27</v>
+      </c>
+      <c r="P15" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>24</v>
+      </c>
+      <c r="R15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="E16" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F16">
         <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="H16" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="I16" t="s">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="J16" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="K16" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="L16" t="s">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="M16" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="N16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O16" t="s">
+        <v>27</v>
+      </c>
+      <c r="P16" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>24</v>
+      </c>
+      <c r="R16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="J17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" t="s">
+        <v>133</v>
+      </c>
+      <c r="L17" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" t="s">
+        <v>24</v>
+      </c>
+      <c r="N17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O17" t="s">
+        <v>27</v>
+      </c>
+      <c r="P17" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>24</v>
+      </c>
+      <c r="R17" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D18" t="s">
+        <v>141</v>
+      </c>
+      <c r="E18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18" t="s">
+        <v>142</v>
+      </c>
+      <c r="I18" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" t="s">
+        <v>143</v>
+      </c>
+      <c r="K18" t="s">
+        <v>60</v>
+      </c>
+      <c r="L18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" t="s">
+        <v>24</v>
+      </c>
+      <c r="N18" t="s">
+        <v>27</v>
+      </c>
+      <c r="O18" t="s">
+        <v>27</v>
+      </c>
+      <c r="P18" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>24</v>
+      </c>
+      <c r="R18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" t="s">
+        <v>147</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19">
         <v>22</v>
       </c>
-      <c r="K17" t="s">
+      <c r="G19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I19" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" t="s">
+        <v>150</v>
+      </c>
+      <c r="K19" t="s">
+        <v>151</v>
+      </c>
+      <c r="L19" t="s">
+        <v>132</v>
+      </c>
+      <c r="M19" t="s">
+        <v>69</v>
+      </c>
+      <c r="N19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" t="s">
+        <v>27</v>
+      </c>
+      <c r="P19" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>24</v>
+      </c>
+      <c r="R19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" t="s">
+        <v>147</v>
+      </c>
+      <c r="E20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" t="s">
+        <v>133</v>
+      </c>
+      <c r="L20" t="s">
+        <v>24</v>
+      </c>
+      <c r="M20" t="s">
+        <v>24</v>
+      </c>
+      <c r="N20" t="s">
+        <v>28</v>
+      </c>
+      <c r="O20" t="s">
+        <v>27</v>
+      </c>
+      <c r="P20" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>24</v>
+      </c>
+      <c r="R20" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D21" t="s">
+        <v>157</v>
+      </c>
+      <c r="E21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" t="s">
+        <v>133</v>
+      </c>
+      <c r="L21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M21" t="s">
+        <v>24</v>
+      </c>
+      <c r="N21" t="s">
+        <v>28</v>
+      </c>
+      <c r="O21" t="s">
+        <v>27</v>
+      </c>
+      <c r="P21" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>24</v>
+      </c>
+      <c r="R21" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="L17" t="s">
+      <c r="B22" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22" t="s">
+        <v>160</v>
+      </c>
+      <c r="E22" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22">
+        <v>25</v>
+      </c>
+      <c r="G22" t="s">
+        <v>161</v>
+      </c>
+      <c r="H22" t="s">
+        <v>162</v>
+      </c>
+      <c r="I22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" t="s">
+        <v>163</v>
+      </c>
+      <c r="K22" t="s">
+        <v>164</v>
+      </c>
+      <c r="L22" t="s">
+        <v>165</v>
+      </c>
+      <c r="M22" t="s">
+        <v>24</v>
+      </c>
+      <c r="N22" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" t="s">
+        <v>27</v>
+      </c>
+      <c r="P22" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>24</v>
+      </c>
+      <c r="R22" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="M17" t="s">
-        <v>23</v>
-      </c>
-      <c r="N17" t="s">
-        <v>120</v>
+      <c r="B23" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" t="s">
+        <v>168</v>
+      </c>
+      <c r="D23" t="s">
+        <v>169</v>
+      </c>
+      <c r="E23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" t="s">
+        <v>165</v>
+      </c>
+      <c r="L23" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" t="s">
+        <v>24</v>
+      </c>
+      <c r="N23" t="s">
+        <v>28</v>
+      </c>
+      <c r="O23" t="s">
+        <v>27</v>
+      </c>
+      <c r="P23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>24</v>
+      </c>
+      <c r="R23" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1887,7 +2666,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1897,17 +2676,22 @@
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="11" width="12" customWidth="1"/>
+    <col min="8" max="8" width="35" customWidth="1"/>
+    <col min="9" max="9" width="8" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>121</v>
+        <v>171</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -1925,716 +2709,1481 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>122</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>123</v>
+        <v>5</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>10</v>
+        <v>172</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I2">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>174</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>131</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G3" t="s">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="H3" t="s">
-        <v>125</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
+        <v>149</v>
+      </c>
+      <c r="I3">
+        <v>22</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" t="s">
+        <v>150</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="E4" t="s">
-        <v>55</v>
+        <v>147</v>
       </c>
       <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>148</v>
+      </c>
+      <c r="H4" t="s">
+        <v>149</v>
+      </c>
+      <c r="I4">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
+        <v>174</v>
+      </c>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" t="s">
+        <v>150</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" t="s">
         <v>28</v>
       </c>
-      <c r="G4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5">
+        <v>19</v>
+      </c>
+      <c r="J5" t="s">
+        <v>174</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" t="s">
+        <v>51</v>
+      </c>
+      <c r="N5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" t="s">
         <v>28</v>
       </c>
-      <c r="G5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
         <v>65</v>
       </c>
-      <c r="C6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s">
+        <v>174</v>
+      </c>
+      <c r="K6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" t="s">
+        <v>67</v>
+      </c>
+      <c r="N6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" t="s">
         <v>28</v>
       </c>
-      <c r="G6" t="s">
-        <v>113</v>
-      </c>
-      <c r="H6" t="s">
-        <v>125</v>
-      </c>
-      <c r="I6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I7">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
+        <v>174</v>
+      </c>
+      <c r="K7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N7" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" t="s">
         <v>28</v>
       </c>
-      <c r="G7" t="s">
-        <v>113</v>
-      </c>
-      <c r="H7" t="s">
-        <v>126</v>
-      </c>
-      <c r="I7" t="s">
-        <v>127</v>
-      </c>
-      <c r="J7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>130</v>
       </c>
       <c r="H8" t="s">
-        <v>128</v>
-      </c>
-      <c r="I8" t="s">
-        <v>127</v>
+        <v>130</v>
+      </c>
+      <c r="I8">
+        <v>17</v>
       </c>
       <c r="J8" t="s">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="K8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="L8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" t="s">
+        <v>131</v>
+      </c>
+      <c r="N8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
+        <v>145</v>
+      </c>
+      <c r="D9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E9" t="s">
+        <v>147</v>
+      </c>
+      <c r="F9" t="s">
         <v>33</v>
       </c>
-      <c r="D9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" t="s">
-        <v>17</v>
-      </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>148</v>
       </c>
       <c r="H9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I9" t="s">
-        <v>23</v>
+        <v>149</v>
+      </c>
+      <c r="I9">
+        <v>22</v>
       </c>
       <c r="J9" t="s">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="K9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="L9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" t="s">
+        <v>150</v>
+      </c>
+      <c r="N9" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="F10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H10" t="s">
+        <v>130</v>
+      </c>
+      <c r="I10">
+        <v>17</v>
+      </c>
+      <c r="J10" t="s">
+        <v>175</v>
+      </c>
+      <c r="K10" t="s">
+        <v>176</v>
+      </c>
+      <c r="L10" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" t="s">
+        <v>131</v>
+      </c>
+      <c r="N10" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" t="s">
         <v>28</v>
       </c>
-      <c r="G10" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" t="s">
-        <v>125</v>
-      </c>
-      <c r="I10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="E11" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K11" t="s">
+        <v>176</v>
+      </c>
+      <c r="L11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N11" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" t="s">
         <v>28</v>
       </c>
-      <c r="G11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H11" t="s">
-        <v>125</v>
-      </c>
-      <c r="I11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>145</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H12" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="I12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J12" t="s">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="K12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="L12" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N12" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>157</v>
       </c>
       <c r="F13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" t="s">
+        <v>177</v>
+      </c>
+      <c r="K13" t="s">
+        <v>178</v>
+      </c>
+      <c r="L13" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" t="s">
+        <v>24</v>
+      </c>
+      <c r="N13" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" t="s">
         <v>28</v>
       </c>
-      <c r="G13" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" t="s">
-        <v>125</v>
-      </c>
-      <c r="I13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J13" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14">
+        <v>17</v>
+      </c>
+      <c r="J14" t="s">
+        <v>174</v>
+      </c>
+      <c r="K14" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" t="s">
+        <v>43</v>
+      </c>
+      <c r="N14" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" t="s">
         <v>28</v>
       </c>
-      <c r="G14" t="s">
-        <v>49</v>
-      </c>
-      <c r="H14" t="s">
-        <v>125</v>
-      </c>
-      <c r="I14" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15">
+        <v>20</v>
+      </c>
+      <c r="J15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K15" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N15" t="s">
+        <v>27</v>
+      </c>
+      <c r="O15" t="s">
         <v>28</v>
       </c>
-      <c r="G15" t="s">
-        <v>56</v>
-      </c>
-      <c r="H15" t="s">
-        <v>125</v>
-      </c>
-      <c r="I15" t="s">
-        <v>23</v>
-      </c>
-      <c r="J15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="F16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" t="s">
+        <v>116</v>
+      </c>
+      <c r="H16" t="s">
+        <v>117</v>
+      </c>
+      <c r="I16">
+        <v>19</v>
+      </c>
+      <c r="J16" t="s">
+        <v>174</v>
+      </c>
+      <c r="K16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" t="s">
+        <v>118</v>
+      </c>
+      <c r="N16" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" t="s">
         <v>28</v>
       </c>
-      <c r="G16" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" t="s">
-        <v>125</v>
-      </c>
-      <c r="I16" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17">
+        <v>17</v>
+      </c>
+      <c r="J17" t="s">
+        <v>174</v>
+      </c>
+      <c r="K17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" t="s">
+        <v>25</v>
+      </c>
+      <c r="N17" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" t="s">
         <v>28</v>
       </c>
-      <c r="G17" t="s">
-        <v>76</v>
-      </c>
-      <c r="H17" t="s">
-        <v>125</v>
-      </c>
-      <c r="I17" t="s">
-        <v>23</v>
-      </c>
-      <c r="J17" t="s">
-        <v>21</v>
-      </c>
-      <c r="K17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="F18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18">
+        <v>19</v>
+      </c>
+      <c r="J18" t="s">
+        <v>174</v>
+      </c>
+      <c r="K18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" t="s">
+        <v>36</v>
+      </c>
+      <c r="N18" t="s">
+        <v>27</v>
+      </c>
+      <c r="O18" t="s">
         <v>28</v>
       </c>
-      <c r="G18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H18" t="s">
-        <v>125</v>
-      </c>
-      <c r="I18" t="s">
-        <v>23</v>
-      </c>
-      <c r="J18" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>164</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="E19" t="s">
-        <v>87</v>
+        <v>160</v>
       </c>
       <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H19" t="s">
+        <v>162</v>
+      </c>
+      <c r="I19">
+        <v>25</v>
+      </c>
+      <c r="J19" t="s">
+        <v>174</v>
+      </c>
+      <c r="K19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" t="s">
+        <v>24</v>
+      </c>
+      <c r="M19" t="s">
+        <v>163</v>
+      </c>
+      <c r="N19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" t="s">
         <v>28</v>
       </c>
-      <c r="G19" t="s">
-        <v>88</v>
-      </c>
-      <c r="H19" t="s">
-        <v>125</v>
-      </c>
-      <c r="I19" t="s">
-        <v>23</v>
-      </c>
-      <c r="J19" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>165</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>160</v>
       </c>
       <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" t="s">
+        <v>161</v>
+      </c>
+      <c r="H20" t="s">
+        <v>162</v>
+      </c>
+      <c r="I20">
+        <v>25</v>
+      </c>
+      <c r="J20" t="s">
+        <v>175</v>
+      </c>
+      <c r="K20" t="s">
+        <v>179</v>
+      </c>
+      <c r="L20" t="s">
+        <v>24</v>
+      </c>
+      <c r="M20" t="s">
+        <v>163</v>
+      </c>
+      <c r="N20" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" t="s">
         <v>28</v>
       </c>
-      <c r="G20" t="s">
-        <v>94</v>
-      </c>
-      <c r="H20" t="s">
-        <v>125</v>
-      </c>
-      <c r="I20" t="s">
-        <v>23</v>
-      </c>
-      <c r="J20" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P20" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>165</v>
       </c>
       <c r="C21" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" t="s">
+        <v>168</v>
+      </c>
+      <c r="E21" t="s">
+        <v>169</v>
+      </c>
+      <c r="F21" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" t="s">
+        <v>177</v>
+      </c>
+      <c r="K21" t="s">
+        <v>179</v>
+      </c>
+      <c r="L21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M21" t="s">
+        <v>24</v>
+      </c>
+      <c r="N21" t="s">
+        <v>27</v>
+      </c>
+      <c r="O21" t="s">
+        <v>28</v>
+      </c>
+      <c r="P21" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" t="s">
+        <v>57</v>
+      </c>
+      <c r="H22" t="s">
+        <v>58</v>
+      </c>
+      <c r="I22">
+        <v>22</v>
+      </c>
+      <c r="J22" t="s">
+        <v>174</v>
+      </c>
+      <c r="K22" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" t="s">
+        <v>24</v>
+      </c>
+      <c r="M22" t="s">
+        <v>59</v>
+      </c>
+      <c r="N22" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" t="s">
+        <v>28</v>
+      </c>
+      <c r="P22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" t="s">
+        <v>65</v>
+      </c>
+      <c r="H23" t="s">
+        <v>66</v>
+      </c>
+      <c r="I23">
+        <v>20</v>
+      </c>
+      <c r="J23" t="s">
+        <v>174</v>
+      </c>
+      <c r="K23" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" t="s">
+        <v>67</v>
+      </c>
+      <c r="N23" t="s">
+        <v>27</v>
+      </c>
+      <c r="O23" t="s">
+        <v>28</v>
+      </c>
+      <c r="P23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" t="s">
+        <v>82</v>
+      </c>
+      <c r="I24">
+        <v>22</v>
+      </c>
+      <c r="J24" t="s">
+        <v>174</v>
+      </c>
+      <c r="K24" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" t="s">
+        <v>83</v>
+      </c>
+      <c r="N24" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" t="s">
+        <v>28</v>
+      </c>
+      <c r="P24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" t="s">
+        <v>87</v>
+      </c>
+      <c r="F25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" t="s">
+        <v>89</v>
+      </c>
+      <c r="I25">
+        <v>19</v>
+      </c>
+      <c r="J25" t="s">
+        <v>174</v>
+      </c>
+      <c r="K25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" t="s">
+        <v>24</v>
+      </c>
+      <c r="M25" t="s">
+        <v>90</v>
+      </c>
+      <c r="N25" t="s">
+        <v>27</v>
+      </c>
+      <c r="O25" t="s">
+        <v>28</v>
+      </c>
+      <c r="P25" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" t="s">
+        <v>96</v>
+      </c>
+      <c r="I26">
+        <v>18</v>
+      </c>
+      <c r="J26" t="s">
+        <v>174</v>
+      </c>
+      <c r="K26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" t="s">
+        <v>24</v>
+      </c>
+      <c r="M26" t="s">
+        <v>97</v>
+      </c>
+      <c r="N26" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" t="s">
+        <v>28</v>
+      </c>
+      <c r="P26" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" t="s">
+        <v>101</v>
+      </c>
+      <c r="F27" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" t="s">
+        <v>102</v>
+      </c>
+      <c r="H27" t="s">
+        <v>103</v>
+      </c>
+      <c r="I27">
+        <v>19</v>
+      </c>
+      <c r="J27" t="s">
+        <v>174</v>
+      </c>
+      <c r="K27" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" t="s">
+        <v>24</v>
+      </c>
+      <c r="M27" t="s">
         <v>104</v>
       </c>
-      <c r="D21" t="s">
+      <c r="N27" t="s">
+        <v>27</v>
+      </c>
+      <c r="O27" t="s">
+        <v>28</v>
+      </c>
+      <c r="P27" t="s">
         <v>105</v>
       </c>
-      <c r="E21" t="s">
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" t="s">
         <v>106</v>
       </c>
-      <c r="F21" t="s">
+      <c r="D28" t="s">
+        <v>107</v>
+      </c>
+      <c r="E28" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" t="s">
+        <v>109</v>
+      </c>
+      <c r="H28" t="s">
+        <v>110</v>
+      </c>
+      <c r="I28">
+        <v>18</v>
+      </c>
+      <c r="J28" t="s">
+        <v>174</v>
+      </c>
+      <c r="K28" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" t="s">
+        <v>24</v>
+      </c>
+      <c r="M28" t="s">
+        <v>111</v>
+      </c>
+      <c r="N28" t="s">
+        <v>27</v>
+      </c>
+      <c r="O28" t="s">
         <v>28</v>
       </c>
-      <c r="G21" t="s">
-        <v>107</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="P28" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" t="s">
+        <v>123</v>
+      </c>
+      <c r="H29" t="s">
+        <v>124</v>
+      </c>
+      <c r="I29">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s">
+        <v>174</v>
+      </c>
+      <c r="K29" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" t="s">
         <v>125</v>
       </c>
-      <c r="I21" t="s">
-        <v>23</v>
-      </c>
-      <c r="J21" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" t="s">
-        <v>22</v>
+      <c r="N29" t="s">
+        <v>27</v>
+      </c>
+      <c r="O29" t="s">
+        <v>28</v>
+      </c>
+      <c r="P29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" t="s">
+        <v>140</v>
+      </c>
+      <c r="E30" t="s">
+        <v>141</v>
+      </c>
+      <c r="F30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30" t="s">
+        <v>88</v>
+      </c>
+      <c r="H30" t="s">
+        <v>142</v>
+      </c>
+      <c r="I30">
+        <v>18</v>
+      </c>
+      <c r="J30" t="s">
+        <v>174</v>
+      </c>
+      <c r="K30" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" t="s">
+        <v>24</v>
+      </c>
+      <c r="M30" t="s">
+        <v>143</v>
+      </c>
+      <c r="N30" t="s">
+        <v>27</v>
+      </c>
+      <c r="O30" t="s">
+        <v>28</v>
+      </c>
+      <c r="P30" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2646,7 +4195,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2666,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
@@ -2678,19 +4227,19 @@
         <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>130</v>
+        <v>181</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>131</v>
+        <v>182</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>132</v>
+        <v>183</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>133</v>
+        <v>184</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>134</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -2698,31 +4247,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G2">
         <v>150</v>
       </c>
       <c r="H2" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -2730,31 +4279,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>191</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="F3" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="G3">
         <v>251</v>
       </c>
       <c r="H3" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -2762,31 +4311,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G4">
         <v>150</v>
       </c>
       <c r="H4" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J4" t="s">
-        <v>146</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2794,31 +4343,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>198</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>199</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>200</v>
       </c>
       <c r="E5" t="s">
-        <v>150</v>
+        <v>201</v>
       </c>
       <c r="F5" t="s">
-        <v>151</v>
+        <v>202</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J5" t="s">
-        <v>152</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -2826,31 +4375,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>204</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>154</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -2858,31 +4407,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>206</v>
       </c>
       <c r="C7" t="s">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>208</v>
       </c>
       <c r="E7" t="s">
-        <v>158</v>
+        <v>209</v>
       </c>
       <c r="F7" t="s">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c r="G7">
         <v>800</v>
       </c>
       <c r="H7" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>160</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -2890,31 +4439,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>161</v>
+        <v>212</v>
       </c>
       <c r="C8" t="s">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>208</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>209</v>
       </c>
       <c r="F8" t="s">
-        <v>162</v>
+        <v>213</v>
       </c>
       <c r="G8">
         <v>3152</v>
       </c>
       <c r="H8" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J8" t="s">
-        <v>163</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -2922,31 +4471,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>164</v>
+        <v>215</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G9">
         <v>250</v>
       </c>
       <c r="H9" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J9" t="s">
-        <v>165</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -2954,31 +4503,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>166</v>
+        <v>217</v>
       </c>
       <c r="C10" t="s">
-        <v>167</v>
+        <v>218</v>
       </c>
       <c r="D10" t="s">
-        <v>168</v>
+        <v>219</v>
       </c>
       <c r="E10" t="s">
-        <v>169</v>
+        <v>220</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G10">
         <v>150</v>
       </c>
       <c r="H10" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J10" t="s">
-        <v>170</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -2986,31 +4535,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>199</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>200</v>
       </c>
       <c r="E11" t="s">
-        <v>150</v>
+        <v>201</v>
       </c>
       <c r="F11" t="s">
-        <v>151</v>
+        <v>202</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J11" t="s">
-        <v>172</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -3018,31 +4567,31 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G12">
         <v>250</v>
       </c>
       <c r="H12" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J12" t="s">
-        <v>174</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -3050,31 +4599,31 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>175</v>
+        <v>226</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J13" t="s">
-        <v>176</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -3082,31 +4631,31 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>177</v>
+        <v>228</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J14" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -3114,31 +4663,31 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>179</v>
+        <v>230</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J15" t="s">
-        <v>180</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -3146,31 +4695,31 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="C16" t="s">
-        <v>148</v>
+        <v>199</v>
       </c>
       <c r="D16" t="s">
-        <v>149</v>
+        <v>200</v>
       </c>
       <c r="E16" t="s">
-        <v>150</v>
+        <v>201</v>
       </c>
       <c r="F16" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G16">
         <v>250</v>
       </c>
       <c r="H16" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16" t="s">
-        <v>182</v>
+        <v>233</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -3178,31 +4727,31 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>235</v>
       </c>
       <c r="G17">
         <v>3</v>
       </c>
       <c r="H17" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J17" t="s">
-        <v>184</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -3210,31 +4759,31 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="C18" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="D18" t="s">
-        <v>187</v>
+        <v>239</v>
       </c>
       <c r="E18" t="s">
-        <v>188</v>
+        <v>240</v>
       </c>
       <c r="F18" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G18">
         <v>250</v>
       </c>
       <c r="H18" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J18" t="s">
-        <v>189</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -3242,31 +4791,31 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>190</v>
+        <v>242</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J19" t="s">
-        <v>191</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -3274,31 +4823,31 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="C20" t="s">
-        <v>148</v>
+        <v>199</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>200</v>
       </c>
       <c r="E20" t="s">
-        <v>150</v>
+        <v>201</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J20" t="s">
-        <v>193</v>
+        <v>245</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -3306,31 +4855,31 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="C21" t="s">
-        <v>148</v>
+        <v>199</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>200</v>
       </c>
       <c r="E21" t="s">
-        <v>150</v>
+        <v>201</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J21" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -3338,31 +4887,31 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>196</v>
+        <v>248</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J22" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -3370,31 +4919,31 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>198</v>
+        <v>250</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F23" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J23" t="s">
-        <v>199</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -3402,31 +4951,31 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F24" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J24" t="s">
-        <v>201</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -3434,31 +4983,31 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F25" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J25" t="s">
-        <v>203</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -3466,31 +5015,31 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>204</v>
+        <v>256</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E26" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F26" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J26" t="s">
-        <v>205</v>
+        <v>257</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -3498,31 +5047,31 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>206</v>
+        <v>258</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E27" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F27" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J27" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -3530,31 +5079,31 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E28" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="F28" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J28" t="s">
-        <v>209</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -3562,31 +5111,31 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>210</v>
+        <v>262</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="E29" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F29" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J29" t="s">
-        <v>211</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -3594,31 +5143,31 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>212</v>
+        <v>264</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D30" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E30" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F30" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J30" t="s">
-        <v>213</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -3626,31 +5175,31 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>214</v>
+        <v>266</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="F31" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J31" t="s">
-        <v>215</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -3658,31 +5207,31 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>216</v>
+        <v>268</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D32" t="s">
-        <v>217</v>
+        <v>269</v>
       </c>
       <c r="E32" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F32" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J32" t="s">
-        <v>218</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -3690,31 +5239,31 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E33" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F33" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J33" t="s">
-        <v>220</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -3722,31 +5271,31 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>221</v>
+        <v>273</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D34" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E34" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F34" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J34" t="s">
-        <v>222</v>
+        <v>274</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -3754,31 +5303,31 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>223</v>
+        <v>275</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D35" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E35" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F35" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J35" t="s">
-        <v>224</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -3786,31 +5335,31 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="C36" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E36" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F36" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="G36">
         <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J36" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -3818,31 +5367,31 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
       <c r="C37" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D37" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E37" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F37" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G37">
         <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="I37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J37" t="s">
-        <v>228</v>
+        <v>280</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -3850,31 +5399,383 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>229</v>
+        <v>281</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="D38" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="E38" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="F38" t="s">
-        <v>230</v>
+        <v>282</v>
       </c>
       <c r="G38">
         <v>2</v>
       </c>
       <c r="H38" t="s">
+        <v>196</v>
+      </c>
+      <c r="I38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J38" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>284</v>
+      </c>
+      <c r="C39" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" t="s">
+        <v>140</v>
+      </c>
+      <c r="E39" t="s">
+        <v>141</v>
+      </c>
+      <c r="F39" t="s">
+        <v>60</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39" t="s">
+        <v>187</v>
+      </c>
+      <c r="I39" t="s">
+        <v>24</v>
+      </c>
+      <c r="J39" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>286</v>
+      </c>
+      <c r="C40" t="s">
+        <v>139</v>
+      </c>
+      <c r="D40" t="s">
+        <v>140</v>
+      </c>
+      <c r="E40" t="s">
+        <v>141</v>
+      </c>
+      <c r="F40" t="s">
+        <v>60</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40" t="s">
+        <v>187</v>
+      </c>
+      <c r="I40" t="s">
+        <v>24</v>
+      </c>
+      <c r="J40" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>288</v>
+      </c>
+      <c r="C41" t="s">
+        <v>139</v>
+      </c>
+      <c r="D41" t="s">
+        <v>140</v>
+      </c>
+      <c r="E41" t="s">
+        <v>141</v>
+      </c>
+      <c r="F41" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>196</v>
+      </c>
+      <c r="I41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J41" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>290</v>
+      </c>
+      <c r="C42" t="s">
         <v>145</v>
       </c>
-      <c r="I38" t="s">
-        <v>23</v>
-      </c>
-      <c r="J38" t="s">
-        <v>231</v>
+      <c r="D42" t="s">
+        <v>146</v>
+      </c>
+      <c r="E42" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" t="s">
+        <v>291</v>
+      </c>
+      <c r="G42">
+        <v>3</v>
+      </c>
+      <c r="H42" t="s">
+        <v>196</v>
+      </c>
+      <c r="I42" t="s">
+        <v>24</v>
+      </c>
+      <c r="J42" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>293</v>
+      </c>
+      <c r="C43" t="s">
+        <v>294</v>
+      </c>
+      <c r="D43" t="s">
+        <v>295</v>
+      </c>
+      <c r="E43" t="s">
+        <v>296</v>
+      </c>
+      <c r="F43" t="s">
+        <v>297</v>
+      </c>
+      <c r="G43">
+        <v>750</v>
+      </c>
+      <c r="H43" t="s">
+        <v>187</v>
+      </c>
+      <c r="I43" t="s">
+        <v>24</v>
+      </c>
+      <c r="J43" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>299</v>
+      </c>
+      <c r="C44" t="s">
+        <v>199</v>
+      </c>
+      <c r="D44" t="s">
+        <v>200</v>
+      </c>
+      <c r="E44" t="s">
+        <v>201</v>
+      </c>
+      <c r="F44" t="s">
+        <v>69</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44" t="s">
+        <v>187</v>
+      </c>
+      <c r="I44" t="s">
+        <v>24</v>
+      </c>
+      <c r="J44" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>301</v>
+      </c>
+      <c r="C45" t="s">
+        <v>199</v>
+      </c>
+      <c r="D45" t="s">
+        <v>200</v>
+      </c>
+      <c r="E45" t="s">
+        <v>201</v>
+      </c>
+      <c r="F45" t="s">
+        <v>202</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
+        <v>187</v>
+      </c>
+      <c r="I45" t="s">
+        <v>24</v>
+      </c>
+      <c r="J45" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>303</v>
+      </c>
+      <c r="C46" t="s">
+        <v>199</v>
+      </c>
+      <c r="D46" t="s">
+        <v>200</v>
+      </c>
+      <c r="E46" t="s">
+        <v>201</v>
+      </c>
+      <c r="F46" t="s">
+        <v>202</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46" t="s">
+        <v>187</v>
+      </c>
+      <c r="I46" t="s">
+        <v>24</v>
+      </c>
+      <c r="J46" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>305</v>
+      </c>
+      <c r="C47" t="s">
+        <v>199</v>
+      </c>
+      <c r="D47" t="s">
+        <v>200</v>
+      </c>
+      <c r="E47" t="s">
+        <v>201</v>
+      </c>
+      <c r="F47" t="s">
+        <v>202</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47" t="s">
+        <v>187</v>
+      </c>
+      <c r="I47" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>307</v>
+      </c>
+      <c r="C48" t="s">
+        <v>199</v>
+      </c>
+      <c r="D48" t="s">
+        <v>200</v>
+      </c>
+      <c r="E48" t="s">
+        <v>201</v>
+      </c>
+      <c r="F48" t="s">
+        <v>202</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48" t="s">
+        <v>187</v>
+      </c>
+      <c r="I48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J48" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>309</v>
+      </c>
+      <c r="C49" t="s">
+        <v>158</v>
+      </c>
+      <c r="D49" t="s">
+        <v>159</v>
+      </c>
+      <c r="E49" t="s">
+        <v>160</v>
+      </c>
+      <c r="F49" t="s">
+        <v>164</v>
+      </c>
+      <c r="G49">
+        <v>1100</v>
+      </c>
+      <c r="H49" t="s">
+        <v>196</v>
+      </c>
+      <c r="I49" t="s">
+        <v>24</v>
+      </c>
+      <c r="J49" t="s">
+        <v>310</v>
       </c>
     </row>
   </sheetData>
